--- a/artfynd/A 40122-2025 artfynd.xlsx
+++ b/artfynd/A 40122-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127735445</v>
       </c>
       <c r="B2" t="n">
-        <v>79609</v>
+        <v>79612</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40122-2025 artfynd.xlsx
+++ b/artfynd/A 40122-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127735445</v>
       </c>
       <c r="B2" t="n">
-        <v>79612</v>
+        <v>79618</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40122-2025 artfynd.xlsx
+++ b/artfynd/A 40122-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127735445</v>
       </c>
       <c r="B2" t="n">
-        <v>79618</v>
+        <v>79621</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40122-2025 artfynd.xlsx
+++ b/artfynd/A 40122-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127735445</v>
       </c>
       <c r="B2" t="n">
-        <v>79621</v>
+        <v>79673</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40122-2025 artfynd.xlsx
+++ b/artfynd/A 40122-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127735445</v>
       </c>
       <c r="B2" t="n">
-        <v>79673</v>
+        <v>79917</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
